--- a/Good_Scrap/Step_1/live_scraped_comics.xlsx
+++ b/Good_Scrap/Step_1/live_scraped_comics.xlsx
@@ -503,17 +503,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Alice In Zombieland</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,27 +528,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1C/pivwouv</t>
+          <t>https://www.comicspriceguide.com/titles/alice-in-zombieland/1B/pivvbxu</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwouv</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Simone Di Meo Variant</t>
+          <t>Cover B by Harvey Tolibao</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -570,17 +570,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Alice In Zombieland</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -595,27 +595,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1-RI-D</t>
+          <t>1-FOCRI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1-RI-D/pivwott</t>
+          <t>https://www.comicspriceguide.com/titles/alice-in-zombieland/1-FOCRI/pivvbxw</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwott</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Greg Land Virgin Variant</t>
+          <t>John Royle Diamond FOC Collectible Cover - Limited 1 for 20</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -637,17 +637,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Alice In Zombieland</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -662,27 +662,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1-RI</t>
+          <t>1C</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1-RI/pivwotu</t>
+          <t>https://www.comicspriceguide.com/titles/alice-in-zombieland/1C/pivvbxt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwotu</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>David Marquez  Variant</t>
+          <t>Cover C by John Royle</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -704,17 +704,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deadpool</t>
+          <t>Butcher Queen: Planet Of The Dead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -729,27 +729,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1J</t>
+          <t>1-WICK</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/deadpool/1J/pivwoww</t>
+          <t>https://www.comicspriceguide.com/titles/butcher-queen-planet-of-the-dead/1-WICK/pivvbvx</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phypju/pivwoww</t>
+          <t>https://www.comicspriceguide.com/image/pkwshv/pivvbvx</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>January 2022</t>
+          <t>September 2020</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Big Time Collectable Exclusive Mike Mayhew Virgin Variant-Limited to 1,000</t>
+          <t>Wicked Gator Comics Exclusive Alan Quah VariantWicked Gator Comics...</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Red 5</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Alice In Zombieland</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -796,27 +796,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1H</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1H/pivwotq</t>
+          <t>https://www.comicspriceguide.com/titles/alice-in-zombieland/1/pivvbxr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwotq</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Greg Land VariantGreg Land Variant</t>
+          <t>Cover A by Igor Vitorino</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>The Edge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2023-Current</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -863,27 +863,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1D</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1D/pivwouy</t>
+          <t>https://www.comicspriceguide.com/titles/the-edge/10/pivvcqr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwouy</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mark Chiarello Foil VariantMark Chiarello Foil...</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Comicsburgh</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Memetic</t>
+          <t>Gi Joe A Real American Hero Duke</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1D</t>
+          <t>1-RI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/memetic/1D/pivwovr</t>
+          <t>https://www.comicspriceguide.com/titles/gi-joe-a-real-american-hero-duke/1-RI/pivvoxp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/wcwrb/pivwovr</t>
+          <t>https://www.comicspriceguide.com/image/pipyoy/pivvoxp</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>October 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Kickstarter James Tynion Decade Anniversary CGC Gold Foil Anniversary Variant-limited to 150</t>
+          <t>Wes Craig B&amp;W Variant</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Boom! Studios</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Free For All</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1-2nd</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1B/pivwouw</t>
+          <t>https://www.comicspriceguide.com/titles/free-for-all/1-2nd/pivvltv</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwouw</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Blank VariantBlank Variant</t>
+          <t>Patrick Horvath Second Printing Variant</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Oni Press</t>
         </is>
       </c>
     </row>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Cosmic Lion Primer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-RI-C</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1-RI-C/pivwotr</t>
+          <t>https://www.comicspriceguide.com/titles/cosmic-lion-primer/1/pivvcqu</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwotr</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Nimit Malavia Black Cat Virgin VariantNimit Malavia Black...</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Cosmic Lion Productions</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deadpool &amp; Wolverine: Wwiii</t>
+          <t>Fire Power</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2020-Current</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1131,27 +1131,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3E</t>
+          <t>19E</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/deadpool-wolverine-wwiii/3E/pivwowv</t>
+          <t>https://www.comicspriceguide.com/titles/fire-power/19E/pivvbvv</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phytmp/pivwowv</t>
+          <t>https://www.comicspriceguide.com/image/pkuxit/pivvbvv</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>September 2024</t>
+          <t>April 2022</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Unknown Comics Exclusive Tyler Kirkham MMA Virgin Variant</t>
+          <t>Comics Vault Live Inhyuk Lee Foil Variant</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Gi Joe A Real American Hero Duke</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2022-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1198,27 +1198,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11-MAYHW-B</t>
+          <t>1-RI-B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/grim/11-MAYHW-B/pivwoqw</t>
+          <t>https://www.comicspriceguide.com/titles/gi-joe-a-real-american-hero-duke/1-RI-B/pivvoxs</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
+          <t>https://www.comicspriceguide.com/image/pipyoy/pivvoxs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2022-Current</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MikeMayhewStudio Exclusive Virgin Variant -Limited to 500</t>
+          <t>Jorge Fornes Foil Letter Variant</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Boom! Studios</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Hatchet: Midnight Murders</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2024-Current</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1265,27 +1265,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1E/pivwoux</t>
+          <t>https://www.comicspriceguide.com/titles/hatchet-midnight-murders/3B/pivvcqq</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwoux</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Nimit Malavia Black Cat VariantNimit Malavia Black...</t>
+          <t>Cover B by Buz Hasson</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>American Mythology</t>
         </is>
       </c>
     </row>
@@ -1307,17 +1307,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Hatchet: Midnight Murders</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2024-Current</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>3C</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1I/pivwotp</t>
+          <t>https://www.comicspriceguide.com/titles/hatchet-midnight-murders/3C/pivvcqp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwotp</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>CAFU Hellgate Variant</t>
+          <t>Cover C by Puis Calzada</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>American Mythology</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>John Carpenter's Tales Of Science Fiction: Pause</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1399,27 +1399,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-RI-B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1-RI-B/pivwots</t>
+          <t>https://www.comicspriceguide.com/titles/john-carpenters-tales-of-science-fiction-pause/3/pivvbvt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwots</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Gil Kane Hidden Gem VariantGil Kane Hidden Gem...</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>Storm King</t>
         </is>
       </c>
     </row>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Amazing Spider-Man</t>
+          <t>Hatchet: Midnight Murders</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2024-Current</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1-RI-E</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/amazing-spider-man/1-RI-E/pivwnvx</t>
+          <t>https://www.comicspriceguide.com/titles/hatchet-midnight-murders/3/pivvbxx</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipwoq/pivwnvx</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>June 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Lee Bermejo Virgin Variant</t>
+          <t>Cover A by Roy Allen Martinez</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,24 +1496,24 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Marvel</t>
+          <t>American Mythology</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Higurashi When They Cry: Meguri</t>
+          <t>Killer Kobra: The Hunt Begins</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/higurashi-when-they-cry-meguri/2soft_cover/pivwcru</t>
+          <t>https://www.comicspriceguide.com/titles/killer-kobra-the-hunt-begins/1B/pivvbyt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover B by Guillermo Fajardo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pop Kill</t>
+          <t>Killer Kobra: The Hunt Begins</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1600,27 +1600,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1D</t>
+          <t>1-FOCRI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/pop-kill/1D/pivwowx</t>
+          <t>https://www.comicspriceguide.com/titles/killer-kobra-the-hunt-begins/1-FOCRI/pivvbyv</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipqbs/pivwowx</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>March 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Will Jack Art Exclusive Cover B Sporty Pop Virgin Variant-Limited to 500</t>
+          <t>Josh Burns Diamond FOC Collection Cover- Limited 1 for 20</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,24 +1630,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Mad Cave Studios</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hakumei &amp; Mikochi: Tiny Little Life In The Woods</t>
+          <t>Killer Kobra: The Hunt Begins</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2018-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1667,27 +1667,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/hakumei-mikochi-tiny-little-life-in-the-woods/12soft_cover/pivwcrq</t>
+          <t>https://www.comicspriceguide.com/titles/killer-kobra-the-hunt-begins/1/pivvbyu</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pjxqir/pivwcrq</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover A by Igor Vitorino</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pop Kill</t>
+          <t>The Legend Of La Rosa Blanca</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/pop-kill/2C/pivwovp</t>
+          <t>https://www.comicspriceguide.com/titles/the-legend-of-la-rosa-blanca/1B/pivvbxy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipqbs/pivwovp</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>March 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Will Jack Art Exclusive Cover A Pop Skirt Virgin Variant-Limited to 600</t>
+          <t>Cover B by Lerix - Full Art Variant</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1764,19 +1764,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Mad Cave Studios</t>
+          <t>American Mythology</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Boy Who Ruled The Monsters</t>
+          <t>Lost Fantasy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1801,17 +1801,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-RI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/the-boy-who-ruled-the-monsters/1soft_cover/pivwcsw</t>
+          <t>https://www.comicspriceguide.com/titles/lost-fantasy/1-RI/pivvlqv</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipviw/pivwcsw</t>
+          <t>https://www.comicspriceguide.com/image/pipymq/pivvlqv</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Luca Casalanguida B&amp;W Variant</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1831,24 +1831,24 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hachioji Specialty: Tengu's Love</t>
+          <t>The Legend Of La Rosa Blanca</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1868,27 +1868,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/the-hachioji-specialty-tengus-love/2soft_cover/pivwcsx</t>
+          <t>https://www.comicspriceguide.com/titles/the-legend-of-la-rosa-blanca/1/pivvbxv</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipviv/pivwcsx</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>December 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover A by Buz Hasson</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1898,24 +1898,24 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>American Mythology</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Higurashi When They Cry: Meguri</t>
+          <t>Lost Fantasy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1935,27 +1935,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1-RI-C</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/higurashi-when-they-cry-meguri/3soft_cover/pivwcrt</t>
+          <t>https://www.comicspriceguide.com/titles/lost-fantasy/1-RI-C/pivvlqx</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phvtos/pivwcrt</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Jae Lee VariantJae Lee Variant</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1965,19 +1965,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hell Is Dark With No Flowers</t>
+          <t>Lost Fantasy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2002,27 +2002,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-RI-B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/hell-is-dark-with-no-flowers/1soft_cover/pivwcrs</t>
+          <t>https://www.comicspriceguide.com/titles/lost-fantasy/1-RI-B/pivvlqy</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipvix/pivwcrs</t>
+          <t>https://www.comicspriceguide.com/image/pipymq/pivvlqy</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Darick Robertson Variant</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2032,29 +2032,29 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gogogogo-Go-Ghost</t>
+          <t>Lost Fantasy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2069,27 +2069,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1-RI-D</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/gogogogo-go-ghost/2soft_cover/pivwcsv</t>
+          <t>https://www.comicspriceguide.com/titles/lost-fantasy/1-RI-D/pivvlpq</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phxslx/pivwcsv</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>November 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Jae Lee Virgin Variant</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pop Kill</t>
+          <t>Nacelleverse: The Great Garloo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2136,27 +2136,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>0-RI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/pop-kill/1E/pivwovq</t>
+          <t>https://www.comicspriceguide.com/titles/nacelleverse-the-great-garloo/0-RI/pivvlwp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipqbs/pivwovq</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>March 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Will Jack Art Exclusive Cover A Sporty Pop Virgin Variant-Limited to 600</t>
+          <t>Ramon Bachs Variant - Limited 1 for 20Ramon Bachs Variant...</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2166,19 +2166,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Mad Cave Studios</t>
+          <t>Oni Press</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Helena And Mr. Big Bad Wolf</t>
+          <t>Relic Hunter</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2188,27 +2188,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/helena-and-mr-big-bad-wolf/1soft_cover/pivwcrp</t>
+          <t>https://www.comicspriceguide.com/titles/relic-hunter/1/pivvcqt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2233,29 +2233,29 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Cosmic Lion Productions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I Want A Gal Gamer To Praise Me</t>
+          <t>Radiant Black</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2021-Current</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2270,27 +2270,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33-RI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/i-want-a-gal-gamer-to-praise-me/3soft_cover/pivwcuw</t>
+          <t>https://www.comicspriceguide.com/titles/radiant-black/33-RI/pivvlpy</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phyqjq/pivwcuw</t>
+          <t>https://www.comicspriceguide.com/image/pkvslq/pivvlpy</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Rod Reis Foil Variant</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2300,19 +2300,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hereditary Triangle</t>
+          <t>Killer Kobra: The Hunt Begins</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1C</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/hereditary-triangle/1soft_cover/pivwcrr</t>
+          <t>https://www.comicspriceguide.com/titles/killer-kobra-the-hunt-begins/1C/pivvbyw</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover C by Josh Burns</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2367,24 +2367,24 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Holy Grail Of Eris</t>
+          <t>Seasons</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2022-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2404,27 +2404,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-RI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/the-holy-grail-of-eris/7soft_cover/pivwcrv</t>
+          <t>https://www.comicspriceguide.com/titles/seasons/4-RI/pivvlsu</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phpxiu/pivwcrv</t>
+          <t>https://www.comicspriceguide.com/image/piqycy/pivvlsu</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>May 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Max Fiumara &amp; Dave Mccaig Variant</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2434,24 +2434,24 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Holox Meeting!</t>
+          <t>Turbo Hawk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/holox-meeting/2soft_cover/pivwcrw</t>
+          <t>https://www.comicspriceguide.com/titles/turbo-hawk/1/pivvcqw</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2501,24 +2501,24 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Cosmic Lion Productions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Holy Grail Of Eris</t>
+          <t>We're Taking Everyone Down With Us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2022-Current</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2538,27 +2538,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2-RI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/the-holy-grail-of-eris/8soft_cover/pivwcry</t>
+          <t>https://www.comicspriceguide.com/titles/were-taking-everyone-down-with-us/2-RI/pivvlry</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phpxiu/pivwcry</t>
+          <t>https://www.comicspriceguide.com/image/pipulu/pivvlry</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>September 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Jorge Fornes Variant</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2568,19 +2568,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I Picked Up This World's Strategy Guide</t>
+          <t>We're Taking Everyone Down With Us</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2605,27 +2605,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1-RI-2nd</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/i-picked-up-this-worlds-strategy-guide/1soft_cover/pivwcuu</t>
+          <t>https://www.comicspriceguide.com/titles/were-taking-everyone-down-with-us/1-RI-2nd/pivvlru</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipvnp/pivwcuu</t>
+          <t>https://www.comicspriceguide.com/image/pipulu/pivvlru</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>February 2025</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2Nd Ptg   Andy Macdonald Variant</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2635,24 +2635,24 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I Want To Be A Receptionist In This Magical World</t>
+          <t>Zenescope Legends</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2023-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2672,27 +2672,27 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2025-FOC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/i-want-to-be-a-receptionist-in-this-magical-world/4soft_cover/pivwcuv</t>
+          <t>https://www.comicspriceguide.com/titles/zenescope-legends/2025-FOC/pivvbxs</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phttcr/pivwcuv</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>June 2024</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Michael Dooney Diamond FOC Collectible Cover - Limited 1 for 20</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Something Is Killing The Children Archive Edition</t>
+          <t>We're Taking Everyone Down With Us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025-Current</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2739,27 +2739,27 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>2-RI-B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/something-is-killing-the-children-archive-edition/1C/pivwovu</t>
+          <t>https://www.comicspriceguide.com/titles/were-taking-everyone-down-with-us/2-RI-B/pivvlrx</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phxvjy/pivwovu</t>
+          <t>https://www.comicspriceguide.com/image/pipulu/pivvlrx</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>September 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Kickstart James Tynion CGC Gold Foil Decade Anniversary Variant</t>
+          <t>Christian Ward Foil Virgin VariantChristian Ward Foil...</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Boom! Studios</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pop Kill</t>
+          <t>Zenescope Legends</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2806,27 +2806,27 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2D</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/pop-kill/2D/pivwovs</t>
+          <t>https://www.comicspriceguide.com/titles/zenescope-legends/2025/pivvbyy</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipqbs/pivwovs</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>March 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Will Jack Art Exclusive Cover B Pop Skirt Virgin Variant-Limited to 500</t>
+          <t>Cover A by Marco Santucci</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2836,29 +2836,29 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mad Cave Studios</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>If The Villainess And Villain Met And Fell In Love</t>
+          <t>Zenescope Legends</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2873,27 +2873,27 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2025B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/if-the-villainess-and-villain-met-and-fell-in-love/1soft_cover/pivwcux</t>
+          <t>https://www.comicspriceguide.com/titles/zenescope-legends/2025B/pivvbyx</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipvns/pivwcux</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>February 2024</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover B by Jordi Tarragona</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2903,29 +2903,29 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>If The Villainess And Villain Met And Fell In Love</t>
+          <t>Zenescope Legends</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2940,27 +2940,27 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2025C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/if-the-villainess-and-villain-met-and-fell-in-love/2soft_cover/pivwctq</t>
+          <t>https://www.comicspriceguide.com/titles/zenescope-legends/2025C/pivvbxq</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipvns/pivwctq</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover C by Michael Dooney</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2970,29 +2970,29 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Hachioji Specialty: Tengu's Love</t>
+          <t>Zenescope Legends</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3007,27 +3007,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2025D</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/the-hachioji-specialty-tengus-love/1soft_cover/pivwcsy</t>
+          <t>https://www.comicspriceguide.com/titles/zenescope-legends/2025D/pivvbxp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/pipviv/pivwcsy</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>August 2024</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cover D by Josh Burns</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3037,24 +3037,24 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Zenescope Entertainment Inc.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Hard Cover</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I Want To Be A Receptionist In This Magical World</t>
+          <t>No Remörse</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2023-Current</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3074,22 +3074,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/i-want-to-be-a-receptionist-in-this-magical-world/5soft_cover/pivwcuy</t>
+          <t>https://www.comicspriceguide.com/titles/no-remorse/1hard_cover/pivvnvt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/image/phttcr/pivwcuy</t>
+          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>September 2024</t>
+          <t>April 2025</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3104,24 +3104,24 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Z2 Comics</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Soft Cover</t>
+          <t>Ashcan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I Cannot Reach You</t>
+          <t>Butcher Queen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2021-Current</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3141,27 +3141,27 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1-SDCC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/titles/i-cannot-reach-you/8soft_cover/pivwcur</t>
+          <t>https://www.comicspriceguide.com/titles/butcher-queen/1-SDCCashcan/pivvbvy</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.comicspriceguide.com/img/missing_lrg.jpg</t>
+          <t>https://www.comicspriceguide.com/image/pksrnr/pivvbvy</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2021-Current</t>
+          <t>July 2019</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SDCC Exclusive Ben Sawyer Ashcan Variant</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Yen Press</t>
+          <t>Red 5</t>
         </is>
       </c>
     </row>
